--- a/schema.xlsx
+++ b/schema.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2abd1f54496c410b/Documents/traffic_accident_project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2abd1f54496c410b/Documents/GCP_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{0F58AD74-71DF-4648-99C1-7A316C3A27ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB213000-2801-48AF-AF90-233276746077}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{0F58AD74-71DF-4648-99C1-7A316C3A27ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A81C4F-DE9F-47B7-AB63-CD17C9E41366}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{5E9A2EEF-4805-4058-AD6D-8C231CAE1D26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>accident_datetime</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -70,31 +70,6 @@
   </si>
   <si>
     <r>
-      <t>accident_latitude</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>accident_longitude</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">B. </t>
     </r>
     <r>
@@ -138,31 +113,6 @@
   </si>
   <si>
     <r>
-      <t>station_latitude</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>station_longitude</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">C. </t>
     </r>
     <r>
@@ -206,8 +156,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>nightmarket_latitude</t>
+    <t>observation_hour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>station_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>accident_id</t>
     </r>
     <r>
       <rPr>
@@ -218,7 +176,7 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> (PK)</t>
     </r>
     <r>
       <rPr>
@@ -227,53 +185,224 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t>nightmarket_longitude</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>accident_id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+      <t xml:space="preserve"> # </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>同事件不同順位會用到這個欄位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>，這個能當成PK嗎</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.流水號編PK   2.再用更多欄位去編PK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accident_longitude</t>
+  </si>
+  <si>
+    <t>accident_latitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>station_longitude</t>
+  </si>
+  <si>
+    <t>station_latitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B C 不同資料來源 以B抓C的資料可能會沒資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>station1_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>station2_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>station_status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>station_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若A找到的測站無資料找第二近的測站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  nightmarket_weekday1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  nightmarket_weekday2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  nightmarket_weekday3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  nightmarket_weekday4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  nightmarket_weekday5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  nightmarket_weekday6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  nightmarket_weekday7</t>
+  </si>
+  <si>
+    <t>nightmarket_bussiness_time_open1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nightmarket_bussiness_time_close1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nightmarket_bussiness_time_open2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nightmarket_bussiness_time_close2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nightmarket_bussiness_time_open3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nightmarket_bussiness_time_close3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> nightmarket_longitude</t>
+  </si>
+  <si>
+    <t>nightmarket_latitude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E. nightmarket_bussiness_hours(營業時間表/fact)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>BigQuery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、MySQL</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
         <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (PK)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>near_accident_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>accident_hour</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>accident_minute</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>observation_hour</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nightmarket_bussiness_hour</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nightmarket_bussiness_minute</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>station_id</t>
+      </rPr>
+      <t>天氣資料放在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>bigquery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>用日期去分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>partition</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無或物 年齡統一:  -1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130歲的人要不要去清理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>accident_to_weather_hour(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>用來比對天氣的時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weekday</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -281,7 +410,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -317,6 +446,26 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -690,118 +839,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA0A8EA-07C0-4FCD-A932-CA1F445C61DB}">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="59.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="2" max="2" width="46.6328125" customWidth="1"/>
+    <col min="3" max="3" width="66.90625" customWidth="1"/>
     <col min="5" max="5" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.5">
+    <row r="1" spans="1:3" ht="18.5">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.5">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" ht="18.5">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="2" t="s">
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="18.5">
-      <c r="A13" s="1" t="s">
+    <row r="10" spans="1:3">
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.5">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>24</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="18.5">
-      <c r="A19" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
-        <v>14</v>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2"/>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
